--- a/monitor_xlsx/20260302.xlsx
+++ b/monitor_xlsx/20260302.xlsx
@@ -94,8 +94,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,6 +544,10 @@
           <t>+2.22%</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,14 +562,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5372.7$</t>
+          <t>5294.4$</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+2.72%</t>
-        </is>
-      </c>
+          <t>+1.22%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,6 +596,10 @@
           <t>+0.43%</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -610,6 +622,10 @@
           <t>+0.48%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -632,6 +648,10 @@
           <t>+7.96%</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -649,6 +669,7 @@
           <t>-389.89億</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>125.36億</t>
@@ -686,6 +707,7 @@
           <t>83.22億</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>33.09億</t>
@@ -696,6 +718,8 @@
           <t>165.45億</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -710,14 +734,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>145.98%</t>
-        </is>
-      </c>
+          <t>111.43%</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>161.75%</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -735,6 +763,11 @@
           <t>-432.14億</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -752,11 +785,15 @@
           <t>14171口</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>11909口</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -774,6 +811,7 @@
           <t>-22.25億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>-52.15億</t>
@@ -786,12 +824,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-14.65億</t>
+          <t>-17.57億</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-292.94億</t>
+          <t>-351.35億</t>
         </is>
       </c>
     </row>
@@ -878,7 +916,10 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -942,7 +983,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-14.65億</t>
+          <t>-17.57億</t>
         </is>
       </c>
     </row>
@@ -954,7 +995,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-292.94億</t>
+          <t>-351.35億</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1076,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1164,31 +1204,18 @@
           <t>0050</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>80.34999999999999</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="F4" t="n">
-        <v>224651</v>
-      </c>
-      <c r="G4" s="7" t="n">
+      <c r="C4" t="inlineStr"/>
+      <c r="G4" s="6" t="n">
         <v>-101500</v>
       </c>
       <c r="H4" t="n">
-        <v>-153600</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>3214</v>
       </c>
       <c r="J4" t="n">
-        <v>30200</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>54837</v>
@@ -1197,17 +1224,14 @@
         <v>8643</v>
       </c>
       <c r="M4" t="n">
-        <v>39383</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>-4134246</v>
       </c>
-      <c r="O4" t="n">
-        <v>1.39</v>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>偏空</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1227,11 +1251,12 @@
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="C5" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
         <v>-967</v>
       </c>
       <c r="H5" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1243,14 +1268,14 @@
         <v>9643</v>
       </c>
       <c r="M5" t="n">
-        <v>49034</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>-27513</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>偏多</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1270,31 +1295,18 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1030</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>-3.74</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3792</v>
-      </c>
-      <c r="G6" s="7" t="n">
+      <c r="C6" t="inlineStr"/>
+      <c r="G6" s="6" t="n">
         <v>-723</v>
       </c>
       <c r="H6" t="n">
-        <v>3870</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>39</v>
       </c>
       <c r="J6" t="n">
-        <v>-898</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>173</v>
@@ -1303,14 +1315,11 @@
         <v>2936</v>
       </c>
       <c r="M6" t="n">
-        <v>14736</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>-78749</v>
       </c>
-      <c r="O6" t="n">
-        <v>2.81</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>中性</t>
@@ -1333,31 +1342,18 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1425</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>-0.35</v>
-      </c>
-      <c r="F7" t="n">
-        <v>15569</v>
-      </c>
-      <c r="G7" s="6" t="n">
+      <c r="C7" t="inlineStr"/>
+      <c r="G7" s="7" t="n">
         <v>210</v>
       </c>
       <c r="H7" t="n">
-        <v>3451</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>162</v>
       </c>
       <c r="J7" t="n">
-        <v>3170</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>337</v>
@@ -1366,17 +1362,14 @@
         <v>6395</v>
       </c>
       <c r="M7" t="n">
-        <v>32825</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>-648849</v>
       </c>
-      <c r="O7" t="n">
-        <v>4.55</v>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>偏多</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1396,31 +1389,18 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1975</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>57404</v>
-      </c>
-      <c r="G8" s="7" t="n">
+      <c r="C8" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
         <v>-19539</v>
       </c>
       <c r="H8" t="n">
-        <v>-37942</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>2624</v>
       </c>
       <c r="J8" t="n">
-        <v>8894</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>1215</v>
@@ -1429,17 +1409,14 @@
         <v>22619</v>
       </c>
       <c r="M8" t="n">
-        <v>108149</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>-6482919</v>
       </c>
-      <c r="O8" t="n">
-        <v>0.87</v>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>偏空</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1459,31 +1436,18 @@
           <t>華邦電</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="F9" t="n">
-        <v>155981</v>
-      </c>
-      <c r="G9" s="6" t="n">
+      <c r="C9" t="inlineStr"/>
+      <c r="G9" s="7" t="n">
         <v>22448</v>
       </c>
       <c r="H9" t="n">
-        <v>26982</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>951</v>
       </c>
       <c r="J9" t="n">
-        <v>25238</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>1504</v>
@@ -1492,17 +1456,14 @@
         <v>132443</v>
       </c>
       <c r="M9" t="n">
-        <v>690462</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>-1111395</v>
       </c>
-      <c r="O9" t="n">
-        <v>6.78</v>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>偏多</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1522,31 +1483,18 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2380</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>-2.46</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3331</v>
-      </c>
-      <c r="G10" s="6" t="n">
+      <c r="C10" t="inlineStr"/>
+      <c r="G10" s="7" t="n">
         <v>182</v>
       </c>
       <c r="H10" t="n">
-        <v>-1656</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>102</v>
       </c>
       <c r="J10" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>157</v>
@@ -1555,17 +1503,14 @@
         <v>1965</v>
       </c>
       <c r="M10" t="n">
-        <v>10930</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>-89480</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.12</v>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>偏空</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1585,31 +1530,18 @@
           <t>世芯-KY</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>3440</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1581</v>
-      </c>
-      <c r="G11" s="6" t="n">
+      <c r="C11" t="inlineStr"/>
+      <c r="G11" s="7" t="n">
         <v>125</v>
       </c>
       <c r="H11" t="n">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>-22</v>
       </c>
       <c r="J11" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>90</v>
@@ -1618,17 +1550,14 @@
         <v>5771</v>
       </c>
       <c r="M11" t="n">
-        <v>29259</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>-19715</v>
       </c>
-      <c r="O11" t="n">
-        <v>0.53</v>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>偏多</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1640,58 +1569,42 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="F12" t="n">
-        <v>26583</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>-4743</v>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="G12" s="6" t="n">
+        <v>-608</v>
       </c>
       <c r="H12" t="n">
-        <v>-9761</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>33</v>
+        <v>590</v>
       </c>
       <c r="J12" t="n">
-        <v>4571</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>796</v>
+        <v>66</v>
       </c>
       <c r="L12" t="n">
-        <v>22324</v>
+        <v>4474</v>
       </c>
       <c r="M12" t="n">
-        <v>119410</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-267422</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-1.2</v>
+        <v>-19080</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>偏空</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1703,58 +1616,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>光聖</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2355</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3957</v>
-      </c>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="G13" s="7" t="n">
-        <v>-608</v>
+        <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>590</v>
+        <v>143</v>
       </c>
       <c r="J13" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="L13" t="n">
-        <v>4474</v>
+        <v>122</v>
       </c>
       <c r="M13" t="n">
-        <v>20998</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-19080</v>
-      </c>
-      <c r="O13" t="n">
-        <v>14.99</v>
+        <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>偏多</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1766,41 +1663,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯亞</t>
-        </is>
-      </c>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="G14" s="6" t="n">
-        <v>132</v>
+        <v>-355</v>
       </c>
       <c r="H14" t="n">
-        <v>-466</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>143</v>
+        <v>-441</v>
       </c>
       <c r="J14" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>454</v>
       </c>
       <c r="L14" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="M14" t="n">
-        <v>-223</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>偏空</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1812,41 +1710,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>威剛</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-355</v>
+          <t>台新科</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>-544</v>
       </c>
       <c r="H15" t="n">
-        <v>-9540</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-441</v>
+        <v>-1</v>
       </c>
       <c r="J15" t="n">
-        <v>-3468</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>454</v>
+        <v>-151</v>
       </c>
       <c r="L15" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M15" t="n">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>主力積極賣出</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -1858,34 +1757,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台新科</t>
-        </is>
-      </c>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="G16" s="7" t="n">
-        <v>-544</v>
+        <v>963</v>
       </c>
       <c r="H16" t="n">
-        <v>989</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-1</v>
+        <v>1179</v>
       </c>
       <c r="J16" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-151</v>
+        <v>-57</v>
       </c>
       <c r="L16" t="n">
-        <v>95</v>
+        <v>-322</v>
       </c>
       <c r="M16" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1904,41 +1804,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>華星光</t>
-        </is>
-      </c>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="G17" s="6" t="n">
-        <v>963</v>
+        <v>-3998</v>
       </c>
       <c r="H17" t="n">
-        <v>1755</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1179</v>
+        <v>-113</v>
       </c>
       <c r="J17" t="n">
-        <v>2798</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-57</v>
+        <v>1261</v>
       </c>
       <c r="L17" t="n">
-        <v>-322</v>
+        <v>19539</v>
       </c>
       <c r="M17" t="n">
-        <v>-1527</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-113508</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>主力積極買進</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -1950,179 +1851,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-3.18</v>
-      </c>
-      <c r="F18" t="n">
-        <v>41298</v>
-      </c>
+          <t>耀登</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="G18" s="7" t="n">
-        <v>-3998</v>
+        <v>278</v>
       </c>
       <c r="H18" t="n">
-        <v>-1341</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-113</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1995</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1261</v>
+        <v>70</v>
       </c>
       <c r="L18" t="n">
-        <v>19539</v>
+        <v>5601</v>
       </c>
       <c r="M18" t="n">
-        <v>98779</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-113508</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.26</v>
+        <v>-11200</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>偏空</t>
+          <t>中性</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4150</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3626</v>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>-21</v>
-      </c>
-      <c r="H19" t="n">
-        <v>685</v>
-      </c>
-      <c r="I19" t="n">
-        <v>300</v>
-      </c>
-      <c r="J19" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>153</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2084</v>
-      </c>
-      <c r="M19" t="n">
-        <v>10773</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-46415</v>
-      </c>
-      <c r="O19" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="E20" t="n">
-        <v>6384</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>278</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-721</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>70</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5601</v>
-      </c>
-      <c r="L20" t="n">
-        <v>23989</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-11200</v>
-      </c>
-      <c r="N20" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/monitor_xlsx/20260302.xlsx
+++ b/monitor_xlsx/20260302.xlsx
@@ -94,8 +94,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>111.43%</t>
+          <t>133.33%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -1204,18 +1204,31 @@
           <t>0050</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="G4" s="6" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F4" t="n">
+        <v>224651</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>-101500</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-153600</v>
       </c>
       <c r="I4" t="n">
         <v>3214</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>30200</v>
       </c>
       <c r="K4" t="n">
         <v>54837</v>
@@ -1224,14 +1237,17 @@
         <v>8643</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>39383</v>
       </c>
       <c r="N4" t="n">
         <v>-4134246</v>
       </c>
+      <c r="O4" t="n">
+        <v>1.39</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏空</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1252,11 +1268,11 @@
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>-967</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1268,14 +1284,14 @@
         <v>9643</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>49034</v>
       </c>
       <c r="N5" t="n">
         <v>-27513</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏多</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1295,18 +1311,31 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="G6" s="6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-3.74</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3792</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>-723</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>3870</v>
       </c>
       <c r="I6" t="n">
         <v>39</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-898</v>
       </c>
       <c r="K6" t="n">
         <v>173</v>
@@ -1315,11 +1344,14 @@
         <v>2936</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>14736</v>
       </c>
       <c r="N6" t="n">
         <v>-78749</v>
       </c>
+      <c r="O6" t="n">
+        <v>2.81</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>中性</t>
@@ -1342,18 +1374,31 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="G7" s="7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1425</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15569</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>210</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>3451</v>
       </c>
       <c r="I7" t="n">
         <v>162</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3170</v>
       </c>
       <c r="K7" t="n">
         <v>337</v>
@@ -1362,14 +1407,17 @@
         <v>6395</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>32825</v>
       </c>
       <c r="N7" t="n">
         <v>-648849</v>
       </c>
+      <c r="O7" t="n">
+        <v>4.55</v>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏多</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1389,18 +1437,31 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="G8" s="6" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1975</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57404</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>-19539</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-37942</v>
       </c>
       <c r="I8" t="n">
         <v>2624</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>8894</v>
       </c>
       <c r="K8" t="n">
         <v>1215</v>
@@ -1409,14 +1470,17 @@
         <v>22619</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>108149</v>
       </c>
       <c r="N8" t="n">
         <v>-6482919</v>
       </c>
+      <c r="O8" t="n">
+        <v>0.87</v>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏空</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1436,18 +1500,31 @@
           <t>華邦電</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="G9" s="7" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F9" t="n">
+        <v>155981</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>22448</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>26982</v>
       </c>
       <c r="I9" t="n">
         <v>951</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>25238</v>
       </c>
       <c r="K9" t="n">
         <v>1504</v>
@@ -1456,14 +1533,17 @@
         <v>132443</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>690462</v>
       </c>
       <c r="N9" t="n">
         <v>-1111395</v>
       </c>
+      <c r="O9" t="n">
+        <v>6.78</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏多</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1483,18 +1563,31 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="G10" s="7" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2380</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3331</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>182</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-1656</v>
       </c>
       <c r="I10" t="n">
         <v>102</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1440</v>
       </c>
       <c r="K10" t="n">
         <v>157</v>
@@ -1503,14 +1596,17 @@
         <v>1965</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>10930</v>
       </c>
       <c r="N10" t="n">
         <v>-89480</v>
       </c>
+      <c r="O10" t="n">
+        <v>3.12</v>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏空</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1530,18 +1626,31 @@
           <t>世芯-KY</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="G11" s="7" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3440</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1581</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>125</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="I11" t="n">
         <v>-22</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="K11" t="n">
         <v>90</v>
@@ -1550,14 +1659,17 @@
         <v>5771</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>29259</v>
       </c>
       <c r="N11" t="n">
         <v>-19715</v>
       </c>
+      <c r="O11" t="n">
+        <v>0.53</v>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏多</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1577,18 +1689,31 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="G12" s="6" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2355</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3957</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>-608</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I12" t="n">
         <v>590</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
         <v>66</v>
@@ -1597,14 +1722,17 @@
         <v>4474</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>20998</v>
       </c>
       <c r="N12" t="n">
         <v>-19080</v>
       </c>
+      <c r="O12" t="n">
+        <v>14.99</v>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏多</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -1624,18 +1752,31 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="G13" s="7" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6399</v>
+      </c>
+      <c r="G13" s="6" t="n">
         <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-466</v>
       </c>
       <c r="I13" t="n">
         <v>143</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="K13" t="n">
         <v>10</v>
@@ -1644,14 +1785,17 @@
         <v>122</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-223</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏空</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1671,18 +1815,31 @@
           <t>威剛</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="G14" s="6" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>262</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-3.32</v>
+      </c>
+      <c r="F14" t="n">
+        <v>16580</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>-355</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-9540</v>
       </c>
       <c r="I14" t="n">
         <v>-441</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-3468</v>
       </c>
       <c r="K14" t="n">
         <v>454</v>
@@ -1691,14 +1848,17 @@
         <v>96</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>主力積極賣出</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -1718,18 +1878,31 @@
           <t>台新科</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="G15" s="6" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>127</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2433</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>-544</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>989</v>
       </c>
       <c r="I15" t="n">
         <v>-1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="K15" t="n">
         <v>-151</v>
@@ -1738,11 +1911,14 @@
         <v>95</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>中性</t>
@@ -1765,18 +1941,31 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="G16" s="7" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4583</v>
+      </c>
+      <c r="G16" s="6" t="n">
         <v>963</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1755</v>
       </c>
       <c r="I16" t="n">
         <v>1179</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2798</v>
       </c>
       <c r="K16" t="n">
         <v>-57</v>
@@ -1785,14 +1974,17 @@
         <v>-322</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1527</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>主力積極買進</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -1812,18 +2004,31 @@
           <t>景碩</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="G17" s="6" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="F17" t="n">
+        <v>41298</v>
+      </c>
+      <c r="G17" s="7" t="n">
         <v>-3998</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-1341</v>
       </c>
       <c r="I17" t="n">
         <v>-113</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1995</v>
       </c>
       <c r="K17" t="n">
         <v>1261</v>
@@ -1832,14 +2037,17 @@
         <v>19539</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>98779</v>
       </c>
       <c r="N17" t="n">
         <v>-113508</v>
       </c>
+      <c r="O17" t="n">
+        <v>0.26</v>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>偏空</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -1859,12 +2067,25 @@
           <t>耀登</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="G18" s="7" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6384</v>
+      </c>
+      <c r="G18" s="6" t="n">
         <v>278</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-347</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1876,14 +2097,17 @@
         <v>5601</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>22351</v>
       </c>
       <c r="N18" t="n">
         <v>-11200</v>
       </c>
+      <c r="O18" t="n">
+        <v>23.16</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>主力積極賣出</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">

--- a/monitor_xlsx/20260302.xlsx
+++ b/monitor_xlsx/20260302.xlsx
@@ -544,10 +544,6 @@
           <t>+2.22%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+1.22%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.43%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.48%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+7.96%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -669,7 +649,6 @@
           <t>-389.89億</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>125.36億</t>
@@ -707,7 +686,6 @@
           <t>83.22億</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>33.09億</t>
@@ -718,8 +696,6 @@
           <t>165.45億</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -737,15 +713,11 @@
           <t>133.33%</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>161.75%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -763,11 +735,6 @@
           <t>-432.14億</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -785,15 +752,11 @@
           <t>14171口</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>11909口</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,7 +774,6 @@
           <t>-22.25億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>-52.15億</t>
@@ -916,10 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1041,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1076,6 +1034,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1267,7 +1226,6 @@
           <t>S&amp;P黃金正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="G5" s="7" t="n">
         <v>-967</v>
       </c>
@@ -2113,6 +2071,112 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1075</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4623</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>731</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3405</v>
+      </c>
+      <c r="H19" t="n">
+        <v>66</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J19" t="n">
+        <v>262</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2246</v>
+      </c>
+      <c r="L19" t="n">
+        <v>12114</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-47592</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1415</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4142</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>409</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-98</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-11</v>
+      </c>
+      <c r="J20" t="n">
+        <v>54</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1903</v>
+      </c>
+      <c r="L20" t="n">
+        <v>9205</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-140153</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
         </is>
       </c>
     </row>

--- a/monitor_xlsx/20260302.xlsx
+++ b/monitor_xlsx/20260302.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2180,165 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>962</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>826</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="G21" t="n">
+        <v>114</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-100</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-31</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>624</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11750</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23</v>
+      </c>
+      <c r="I22" t="n">
+        <v>23</v>
+      </c>
+      <c r="J22" t="n">
+        <v>79</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-96</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-241</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1515</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10658</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>-389</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3511</v>
+      </c>
+      <c r="H23" t="n">
+        <v>522</v>
+      </c>
+      <c r="I23" t="n">
+        <v>669</v>
+      </c>
+      <c r="J23" t="n">
+        <v>216</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2071</v>
+      </c>
+      <c r="L23" t="n">
+        <v>7741</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-106265</v>
+      </c>
+      <c r="N23" t="n">
+        <v>37.24</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260302.xlsx
+++ b/monitor_xlsx/20260302.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2339,6 +2339,59 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>245.5</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8576</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>649</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4017</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23</v>
+      </c>
+      <c r="J24" t="n">
+        <v>204</v>
+      </c>
+      <c r="K24" t="n">
+        <v>8011</v>
+      </c>
+      <c r="L24" t="n">
+        <v>33235</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-58741</v>
+      </c>
+      <c r="N24" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
